--- a/public/tool/app/http-lock-entry-helper/template.xlsx
+++ b/public/tool/app/http-lock-entry-helper/template.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入模板" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="锁班数据" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="类型列表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'输入模板'!$A$1:$K$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -415,20 +414,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,39 +450,411 @@
           <t>结束日期</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>时间模式</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>开始时间</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>结束时间</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>锁班日期</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>备注</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>000000</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ALV-年假（公休假）</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="无效输入" error="请从下拉列表选择" type="list">
+      <formula1>类型列表!$A$1:$A$51</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ALV-年假（公休假）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ALV_FD-飞行员公休（订座）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RECU_LVE-健康疗养</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RECU_LVE_R-康复疗养</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MAT_FA_LVE-陪产假</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MAT_MO_LVE-产假</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PREGNANT-孕假</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PARENT_LVE-探亲假-探父母</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SPOUSE_LVE-探亲假-探配偶</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MARR_LVE-婚假</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>COMP_LVE-丧假</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHILD_LVE-育儿假</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INJURY_LVE-工伤假</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LWOP_LVE-其他（事假）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UNPAID_LVE-无薪</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HOUSE_LVE-搬家</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BREED_LVE-哺乳假</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PATERNITY-独生子女护理假</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BIRC_LVE-计划生育假</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>REWARD_LVE-奖励</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PENALTY-停飞</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PRD_LVE-经期假</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GRD-地面班</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GDO-地面休息</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TRNG1-训练</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BS_STUDY-业务学习</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BUSINESS-公务</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>GRD_ONDUTY-地面值班</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LG_STUDY-语言学习/考试</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MEDL_CHK-体检_临床</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MEDL_PHLE-体检_抽血</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MEDL_EET-体检_平板</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MEDL_PSYC-体检_心理测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MTG-会议</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MTG_SF-安全讲评会</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DGET-危险品培训</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EP-飞行人员应急复训</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CRM-CRM培训</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>T_SIM_INS-模拟机检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>T_SIM_REC-模拟机复训</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>T_SIM_INT-模拟机初始</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>T_SIM_UPG-模拟机升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>T_SIM_CON-模拟机_转机型</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MAKEUP-补考</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BS_CONCL-飞行后讲评</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BS_CHK-业务检查</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ADMN-管理任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SOCIAL-社会活动</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>HANDBOOK-手册</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>POL_STUDY-政治学习</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T/A-部门活动</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>